--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S.A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69587C73-41E6-4E95-BB43-FB6FE5B99C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEA4124-695D-4AC9-9E53-7217EBA615F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="211">
   <si>
     <t>מזהה</t>
   </si>
@@ -663,6 +663,9 @@
   </si>
   <si>
     <t>שבע דהן</t>
+  </si>
+  <si>
+    <t>בוגרת</t>
   </si>
 </sst>
 </file>
@@ -2376,7 +2379,7 @@
         <v>194</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>87</v>
@@ -2394,7 +2397,7 @@
         <v>196</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>88</v>
@@ -2412,7 +2415,7 @@
         <v>197</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>89</v>
@@ -2430,7 +2433,7 @@
         <v>9</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>90</v>
@@ -2448,7 +2451,7 @@
         <v>200</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>91</v>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S.A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEA4124-695D-4AC9-9E53-7217EBA615F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B823F48-2B9F-40D2-92AF-537C4E0EDA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,21 +68,9 @@
     <t>י'2</t>
   </si>
   <si>
-    <t>יא'1</t>
-  </si>
-  <si>
-    <t>יא'2</t>
-  </si>
-  <si>
     <t>יונתן</t>
   </si>
   <si>
-    <t>יב'1</t>
-  </si>
-  <si>
-    <t>יב'2</t>
-  </si>
-  <si>
     <t>שירה</t>
   </si>
   <si>
@@ -666,6 +654,18 @@
   </si>
   <si>
     <t>בוגרת</t>
+  </si>
+  <si>
+    <t>י"א'1</t>
+  </si>
+  <si>
+    <t>י"א'2</t>
+  </si>
+  <si>
+    <t>י"ב'1</t>
+  </si>
+  <si>
+    <t>י"ב'2</t>
   </si>
 </sst>
 </file>
@@ -777,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -786,9 +786,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1151,199 +1148,199 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>336593033</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>92</v>
+      <c r="C2" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>221333933</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>94</v>
+      <c r="C3" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>221304124</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>21</v>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>222015075</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>96</v>
+      <c r="C5" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>222238008</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>98</v>
+      <c r="C6" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>334911419</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>100</v>
+      <c r="C7" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>221100654</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>221326721</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>102</v>
+      <c r="C9" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>34</v>
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>221329352</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>104</v>
+      <c r="C10" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>337337984</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>106</v>
+      <c r="C11" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="5">
+        <v>20</v>
+      </c>
+      <c r="F11" s="4">
         <v>528199977</v>
       </c>
     </row>
@@ -1351,1110 +1348,1110 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>335219473</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>108</v>
+      <c r="C12" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>335721833</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>110</v>
+      <c r="C13" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>37</v>
+        <v>21</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>336198973</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>112</v>
+      <c r="C14" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>335650057</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>114</v>
+      <c r="C15" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>220173835</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>116</v>
+      <c r="C16" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>40</v>
+        <v>21</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>335710794</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>117</v>
+      <c r="C17" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>335811634</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>119</v>
+      <c r="C18" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>42</v>
+        <v>22</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>335659033</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>335733226</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>121</v>
+      <c r="C20" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>44</v>
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>334576683</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>16</v>
+      <c r="C21" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>45</v>
+        <v>22</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>220414544</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>124</v>
+      <c r="C22" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>46</v>
+        <v>22</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <v>219454675</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>126</v>
+      <c r="C23" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>47</v>
+        <v>22</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>334516796</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>128</v>
+      <c r="C24" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>48</v>
+      <c r="F24" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>334651023</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>130</v>
+      <c r="C25" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="5"/>
+      <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>334613866</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>110</v>
+      <c r="C26" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>49</v>
+      <c r="F26" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>333529246</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>132</v>
+      <c r="C27" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>50</v>
+      <c r="F27" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>334251030</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>134</v>
+      <c r="C28" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>51</v>
+      <c r="F28" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>334089570</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>136</v>
+      <c r="C29" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>52</v>
+      <c r="F29" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>334961521</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>138</v>
+      <c r="C30" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>53</v>
+      <c r="F30" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>335017299</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>140</v>
+      <c r="C31" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>54</v>
+      <c r="F31" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>217734839</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>142</v>
+      <c r="C32" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>55</v>
+      <c r="F32" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>219007614</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>144</v>
+      <c r="C33" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>56</v>
+      <c r="F33" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>331922633</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>146</v>
+      <c r="C34" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>57</v>
+      <c r="F34" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>334670056</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>148</v>
+      <c r="C35" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>58</v>
+      <c r="F35" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>218594620</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>150</v>
+      <c r="C36" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>59</v>
+        <v>207</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>333007839</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>152</v>
+      <c r="C37" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>60</v>
+        <v>207</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="6">
         <v>333154722</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>101</v>
+      <c r="C38" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>61</v>
+        <v>207</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="4">
         <v>333313518</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>154</v>
+      <c r="C39" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>62</v>
+        <v>207</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>217460351</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>156</v>
+      <c r="C40" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>63</v>
+        <v>207</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="4">
         <v>330853318</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>158</v>
+      <c r="C41" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>64</v>
+        <v>207</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="6">
         <v>333432052</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>160</v>
+      <c r="C42" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>65</v>
+        <v>207</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="5">
         <v>333514750</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>162</v>
+      <c r="C43" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>66</v>
+        <v>207</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="4">
         <v>218707263</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>163</v>
+      <c r="C44" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>67</v>
+        <v>207</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="4">
         <v>334061090</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>165</v>
+      <c r="C45" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>68</v>
+        <v>208</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="4">
         <v>218899532</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="11"/>
+      <c r="B47" s="4">
+        <v>333085876</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="11"/>
+      <c r="B48" s="4">
+        <v>218971745</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="11"/>
+      <c r="B49" s="4">
+        <v>217613959</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="5" t="s">
+      <c r="D49" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="11"/>
+      <c r="B50" s="4">
+        <v>217687425</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="11"/>
+      <c r="B51" s="4">
+        <v>218478204</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="12"/>
-      <c r="B47" s="5">
-        <v>333085876</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" s="12" t="s">
+    <row r="52" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A52" s="11"/>
+      <c r="B52" s="4">
+        <v>331125971</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="11"/>
+      <c r="B53" s="4">
+        <v>217097120</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="11"/>
+      <c r="B54" s="4">
+        <v>214116295</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="11"/>
+      <c r="B55" s="4">
+        <v>216676254</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A56" s="11"/>
+      <c r="B56" s="4">
+        <v>217221167</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A57" s="11"/>
+      <c r="B57" s="8">
+        <v>333246916</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="11"/>
+      <c r="B58" s="4">
+        <v>333072312</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A59" s="11"/>
+      <c r="B59" s="4">
+        <v>328223110</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A60" s="11"/>
+      <c r="B60" s="4">
+        <v>329656623</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="11"/>
+      <c r="B61" s="4">
+        <v>218048148</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A62" s="11"/>
+      <c r="B62" s="4">
+        <v>331762377</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A63" s="11"/>
+      <c r="B63" s="4">
+        <v>331566588</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="11"/>
+      <c r="B64" s="4">
+        <v>330834623</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="11"/>
+      <c r="B65" s="7">
+        <v>216678912</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="12"/>
-      <c r="B48" s="5">
-        <v>218971745</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="12"/>
-      <c r="B49" s="5">
-        <v>217613959</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="12"/>
-      <c r="B50" s="5">
-        <v>217687425</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A51" s="12"/>
-      <c r="B51" s="5">
-        <v>218478204</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="12"/>
-      <c r="B52" s="5">
-        <v>331125971</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="12"/>
-      <c r="B53" s="5">
-        <v>217097120</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="12"/>
-      <c r="B54" s="5">
-        <v>214116295</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="12"/>
-      <c r="B55" s="5">
-        <v>216676254</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A56" s="12"/>
-      <c r="B56" s="5">
-        <v>217221167</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="12" t="s">
+      <c r="F65" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A66" s="11"/>
+      <c r="B66" s="7">
+        <v>216833244</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A67" s="11"/>
+      <c r="B67" s="7">
+        <v>330641135</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="12"/>
-      <c r="B57" s="9">
-        <v>333246916</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="12"/>
-      <c r="B58" s="5">
-        <v>333072312</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A59" s="12"/>
-      <c r="B59" s="5">
-        <v>328223110</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A60" s="12"/>
-      <c r="B60" s="5">
-        <v>329656623</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="12"/>
-      <c r="B61" s="5">
-        <v>218048148</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A62" s="12"/>
-      <c r="B62" s="5">
-        <v>331762377</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A63" s="12"/>
-      <c r="B63" s="5">
-        <v>331566588</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" s="5" t="s">
+      <c r="D67" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F67" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A64" s="12"/>
-      <c r="B64" s="5">
-        <v>330834623</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" s="5" t="s">
+    <row r="68" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="11"/>
+      <c r="B68" s="7">
+        <v>216334649</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F68" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A65" s="12"/>
-      <c r="B65" s="8">
-        <v>216678912</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F65" s="8" t="s">
+    <row r="69" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A69" s="11"/>
+      <c r="B69" s="7">
+        <v>216118000</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F69" s="7" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="12"/>
-      <c r="B66" s="8">
-        <v>216833244</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A67" s="12"/>
-      <c r="B67" s="8">
-        <v>330641135</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A68" s="12"/>
-      <c r="B68" s="8">
-        <v>216334649</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A69" s="12"/>
-      <c r="B69" s="8">
-        <v>216118000</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S.A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B823F48-2B9F-40D2-92AF-537C4E0EDA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110C3FC6-F7D1-402C-AD7E-1F50A37F0C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -656,16 +656,16 @@
     <t>בוגרת</t>
   </si>
   <si>
-    <t>י"א'1</t>
-  </si>
-  <si>
-    <t>י"א'2</t>
-  </si>
-  <si>
-    <t>י"ב'1</t>
-  </si>
-  <si>
-    <t>י"ב'2</t>
+    <t>י״א 1</t>
+  </si>
+  <si>
+    <t>י״א 2</t>
+  </si>
+  <si>
+    <t>י״ב 1</t>
+  </si>
+  <si>
+    <t>י״ב 2</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1835,7 @@
       <c r="D36" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" t="s">
         <v>207</v>
       </c>
       <c r="F36" s="4" t="s">
@@ -1855,7 +1855,7 @@
       <c r="D37" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" t="s">
         <v>207</v>
       </c>
       <c r="F37" s="4" t="s">
@@ -1875,7 +1875,7 @@
       <c r="D38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" t="s">
         <v>207</v>
       </c>
       <c r="F38" s="6" t="s">
@@ -1895,7 +1895,7 @@
       <c r="D39" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" t="s">
         <v>207</v>
       </c>
       <c r="F39" s="4" t="s">
@@ -1915,7 +1915,7 @@
       <c r="D40" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" t="s">
         <v>207</v>
       </c>
       <c r="F40" s="4" t="s">
@@ -1935,7 +1935,7 @@
       <c r="D41" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" t="s">
         <v>207</v>
       </c>
       <c r="F41" s="4" t="s">
@@ -1955,7 +1955,7 @@
       <c r="D42" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" t="s">
         <v>207</v>
       </c>
       <c r="F42" s="6" t="s">
@@ -1975,7 +1975,7 @@
       <c r="D43" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" t="s">
         <v>207</v>
       </c>
       <c r="F43" s="5" t="s">
@@ -1995,7 +1995,7 @@
       <c r="D44" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" t="s">
         <v>207</v>
       </c>
       <c r="F44" s="4" t="s">
@@ -2015,7 +2015,7 @@
       <c r="D45" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" t="s">
         <v>208</v>
       </c>
       <c r="F45" s="4" t="s">
@@ -2035,14 +2035,14 @@
       <c r="D46" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" t="s">
         <v>208</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A47" s="11"/>
       <c r="B47" s="4">
         <v>333085876</v>
@@ -2053,12 +2053,12 @@
       <c r="D47" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" t="s">
         <v>208</v>
       </c>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A48" s="11"/>
       <c r="B48" s="4">
         <v>218971745</v>
@@ -2069,14 +2069,14 @@
       <c r="D48" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" t="s">
         <v>208</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A49" s="11"/>
       <c r="B49" s="4">
         <v>217613959</v>
@@ -2087,14 +2087,14 @@
       <c r="D49" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" t="s">
         <v>208</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="11"/>
       <c r="B50" s="4">
         <v>217687425</v>
@@ -2105,14 +2105,14 @@
       <c r="D50" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" t="s">
         <v>208</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A51" s="11"/>
       <c r="B51" s="4">
         <v>218478204</v>
@@ -2123,14 +2123,14 @@
       <c r="D51" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" t="s">
         <v>208</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A52" s="11"/>
       <c r="B52" s="4">
         <v>331125971</v>
@@ -2141,14 +2141,14 @@
       <c r="D52" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" t="s">
         <v>209</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A53" s="11"/>
       <c r="B53" s="4">
         <v>217097120</v>
@@ -2159,14 +2159,14 @@
       <c r="D53" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" t="s">
         <v>209</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A54" s="11"/>
       <c r="B54" s="4">
         <v>214116295</v>
@@ -2177,14 +2177,14 @@
       <c r="D54" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" t="s">
         <v>209</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A55" s="11"/>
       <c r="B55" s="4">
         <v>216676254</v>
@@ -2195,14 +2195,14 @@
       <c r="D55" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" t="s">
         <v>209</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A56" s="11"/>
       <c r="B56" s="4">
         <v>217221167</v>
@@ -2213,14 +2213,14 @@
       <c r="D56" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" t="s">
         <v>209</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A57" s="11"/>
       <c r="B57" s="8">
         <v>333246916</v>
@@ -2231,14 +2231,14 @@
       <c r="D57" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" t="s">
         <v>209</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A58" s="11"/>
       <c r="B58" s="4">
         <v>333072312</v>
@@ -2249,14 +2249,14 @@
       <c r="D58" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" t="s">
         <v>210</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A59" s="11"/>
       <c r="B59" s="4">
         <v>328223110</v>
@@ -2267,14 +2267,14 @@
       <c r="D59" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" t="s">
         <v>210</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A60" s="11"/>
       <c r="B60" s="4">
         <v>329656623</v>
@@ -2285,14 +2285,14 @@
       <c r="D60" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" t="s">
         <v>210</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="11"/>
       <c r="B61" s="4">
         <v>218048148</v>
@@ -2303,14 +2303,14 @@
       <c r="D61" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" t="s">
         <v>210</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A62" s="11"/>
       <c r="B62" s="4">
         <v>331762377</v>
@@ -2321,14 +2321,14 @@
       <c r="D62" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" t="s">
         <v>210</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A63" s="11"/>
       <c r="B63" s="4">
         <v>331566588</v>
@@ -2339,14 +2339,14 @@
       <c r="D63" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" t="s">
         <v>210</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A64" s="11"/>
       <c r="B64" s="4">
         <v>330834623</v>
@@ -2357,7 +2357,7 @@
       <c r="D64" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" t="s">
         <v>210</v>
       </c>
       <c r="F64" s="4" t="s">

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S.A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110C3FC6-F7D1-402C-AD7E-1F50A37F0C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4736F5-069C-4B10-AB01-2422957D303A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,18 +56,12 @@
     <t>אורי</t>
   </si>
   <si>
-    <t>י'1</t>
-  </si>
-  <si>
     <t>מיכל</t>
   </si>
   <si>
     <t>אברהם</t>
   </si>
   <si>
-    <t>י'2</t>
-  </si>
-  <si>
     <t>יונתן</t>
   </si>
   <si>
@@ -666,6 +660,12 @@
   </si>
   <si>
     <t>י״ב 2</t>
+  </si>
+  <si>
+    <t>אי' 1</t>
+  </si>
+  <si>
+    <t>אי' 2</t>
   </si>
 </sst>
 </file>
@@ -1152,16 +1152,16 @@
         <v>336593033</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1172,16 +1172,16 @@
         <v>221333933</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1192,16 +1192,16 @@
         <v>221304124</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1212,16 +1212,16 @@
         <v>222015075</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1232,16 +1232,16 @@
         <v>222238008</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1252,16 +1252,16 @@
         <v>334911419</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1272,16 +1272,16 @@
         <v>221100654</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1292,16 +1292,16 @@
         <v>221326721</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1312,16 +1312,16 @@
         <v>221329352</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1332,13 +1332,13 @@
         <v>337337984</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11" s="4">
         <v>528199977</v>
@@ -1352,16 +1352,16 @@
         <v>335219473</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1372,16 +1372,16 @@
         <v>335721833</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1392,16 +1392,16 @@
         <v>336198973</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1412,16 +1412,16 @@
         <v>335650057</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1432,16 +1432,16 @@
         <v>220173835</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1452,16 +1452,16 @@
         <v>335710794</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1472,16 +1472,16 @@
         <v>335811634</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1495,13 +1495,13 @@
         <v>6</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1512,16 +1512,16 @@
         <v>335733226</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1532,16 +1532,16 @@
         <v>334576683</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1552,16 +1552,16 @@
         <v>220414544</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1572,16 +1572,16 @@
         <v>219454675</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1592,16 +1592,16 @@
         <v>334516796</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1612,13 +1612,13 @@
         <v>334651023</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -1630,16 +1630,16 @@
         <v>334613866</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1650,16 +1650,16 @@
         <v>333529246</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1670,16 +1670,16 @@
         <v>334251030</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1690,16 +1690,16 @@
         <v>334089570</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1710,16 +1710,16 @@
         <v>334961521</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1730,16 +1730,16 @@
         <v>335017299</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1750,16 +1750,16 @@
         <v>217734839</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1770,16 +1770,16 @@
         <v>219007614</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1790,16 +1790,16 @@
         <v>331922633</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1810,16 +1810,16 @@
         <v>334670056</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1830,16 +1830,16 @@
         <v>218594620</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1850,16 +1850,16 @@
         <v>333007839</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1870,16 +1870,16 @@
         <v>333154722</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1890,16 +1890,16 @@
         <v>333313518</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1910,16 +1910,16 @@
         <v>217460351</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1930,16 +1930,16 @@
         <v>330853318</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E41" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1950,16 +1950,16 @@
         <v>333432052</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E42" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1970,16 +1970,16 @@
         <v>333514750</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -1990,16 +1990,16 @@
         <v>218707263</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -2010,16 +2010,16 @@
         <v>334061090</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -2030,16 +2030,16 @@
         <v>218899532</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E46" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2048,13 +2048,13 @@
         <v>333085876</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E47" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F47" s="4"/>
     </row>
@@ -2064,16 +2064,16 @@
         <v>218971745</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E48" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2082,16 +2082,16 @@
         <v>217613959</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E49" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2100,16 +2100,16 @@
         <v>217687425</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E50" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2118,16 +2118,16 @@
         <v>218478204</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E51" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2136,16 +2136,16 @@
         <v>331125971</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E52" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2154,16 +2154,16 @@
         <v>217097120</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E53" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2172,16 +2172,16 @@
         <v>214116295</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2190,16 +2190,16 @@
         <v>216676254</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E55" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2208,16 +2208,16 @@
         <v>217221167</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2226,16 +2226,16 @@
         <v>333246916</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E57" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2244,16 +2244,16 @@
         <v>333072312</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2262,16 +2262,16 @@
         <v>328223110</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2280,16 +2280,16 @@
         <v>329656623</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2298,16 +2298,16 @@
         <v>218048148</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E61" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2316,16 +2316,16 @@
         <v>331762377</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2334,16 +2334,16 @@
         <v>331566588</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
@@ -2352,16 +2352,16 @@
         <v>330834623</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E64" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -2370,16 +2370,16 @@
         <v>216678912</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -2388,16 +2388,16 @@
         <v>216833244</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -2406,16 +2406,16 @@
         <v>330641135</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -2424,16 +2424,16 @@
         <v>216334649</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
@@ -2442,16 +2442,16 @@
         <v>216118000</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
